--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8774F99-777D-4566-B0BB-2BC04DF260F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EA2557-4D9D-4F06-B583-838A40931158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
